--- a/서류리스트.xlsx
+++ b/서류리스트.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\smart-logstics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C715666E-4F14-46D7-BC30-E503E8E0A3FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE85E56-3BBB-4D53-A6E3-3D56D054886E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C722C9AC-CAB8-40C6-8CCB-1BE659AFD812}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="37">
   <si>
     <t>필요서류 리스트</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -131,10 +131,6 @@
   </si>
   <si>
     <t>비고</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20260713 전달예정(김성은님)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -168,6 +164,18 @@
   <si>
     <t>자체평가표 1부(스마트물류센터 인증요령 
 별표 1.2 스마트물류센터(일반/택배) 인증 평가 영역별 자체평가점수표)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260710 공유(강호성님)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260710 공유(정유림님)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20260713 공유예정(김성은님)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -199,12 +207,18 @@
       <scheme val="major"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -236,7 +250,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -256,6 +270,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -622,16 +645,16 @@
         <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="E3" s="6" t="s">
         <v>31</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>32</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>7</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="H3" s="5" t="s">
         <v>25</v>
@@ -649,7 +672,7 @@
       <c r="E4" s="6"/>
       <c r="F4" s="5"/>
       <c r="G4" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H4" s="5"/>
     </row>
@@ -665,7 +688,7 @@
       <c r="E5" s="6"/>
       <c r="F5" s="5"/>
       <c r="G5" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H5" s="5"/>
     </row>
@@ -681,49 +704,61 @@
       <c r="E6" s="6"/>
       <c r="F6" s="5"/>
       <c r="G6" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H6" s="5"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="5">
+      <c r="A7" s="7">
         <v>4</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="C7" s="5"/>
-      <c r="D7" s="6"/>
-      <c r="E7" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F7" s="5" t="s">
+      <c r="C7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="9">
+        <v>46213</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H7" s="5"/>
+      <c r="G7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="5">
+      <c r="A8" s="7">
         <v>5</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="5"/>
-      <c r="D8" s="6"/>
-      <c r="E8" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F8" s="5" t="s">
+      <c r="C8" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="9">
+        <v>46213</v>
+      </c>
+      <c r="E8" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="H8" s="5"/>
+      <c r="G8" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
@@ -737,7 +772,7 @@
       <c r="E9" s="6"/>
       <c r="F9" s="5"/>
       <c r="G9" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H9" s="5"/>
     </row>
@@ -746,14 +781,14 @@
         <v>7</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="6"/>
       <c r="E10" s="6"/>
       <c r="F10" s="5"/>
       <c r="G10" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H10" s="5"/>
     </row>
@@ -769,7 +804,7 @@
       <c r="E11" s="6"/>
       <c r="F11" s="5"/>
       <c r="G11" s="5" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="H11" s="5"/>
     </row>
@@ -785,7 +820,7 @@
       <c r="E12" s="6"/>
       <c r="F12" s="5"/>
       <c r="G12" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H12" s="5"/>
     </row>
@@ -801,7 +836,7 @@
       <c r="E13" s="6"/>
       <c r="F13" s="5"/>
       <c r="G13" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H13" s="5"/>
     </row>
@@ -819,13 +854,13 @@
         <v>46213</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>23</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H14" s="5"/>
     </row>
@@ -843,13 +878,13 @@
         <v>46213</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>23</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H15" s="5"/>
     </row>
@@ -867,13 +902,13 @@
         <v>46213</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>23</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H16" s="5"/>
     </row>
@@ -891,16 +926,16 @@
         <v>46213</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.3">
@@ -917,16 +952,16 @@
         <v>46213</v>
       </c>
       <c r="E18" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F18" s="5" t="s">
         <v>24</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.3">
@@ -943,39 +978,41 @@
         <v>46213</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F19" s="5" t="s">
         <v>23</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H19" s="5"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A20" s="5">
+      <c r="A20" s="7">
         <v>17</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B20" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D20" s="6">
+      <c r="D20" s="9">
         <v>46213</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="5" t="s">
+      <c r="E20" s="9" t="s">
+        <v>32</v>
+      </c>
+      <c r="F20" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="G20" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="H20" s="5"/>
+      <c r="G20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="H20" s="7" t="s">
+        <v>34</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/서류리스트.xlsx
+++ b/서류리스트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\smart-logstics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE85E56-3BBB-4D53-A6E3-3D56D054886E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD063710-9C8A-4CB2-A801-459359A4FF29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{C722C9AC-CAB8-40C6-8CCB-1BE659AFD812}"/>
+    <workbookView xWindow="-15420" yWindow="16080" windowWidth="29040" windowHeight="17520" xr2:uid="{C722C9AC-CAB8-40C6-8CCB-1BE659AFD812}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="39">
   <si>
     <t>필요서류 리스트</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -175,7 +175,15 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>20260713 공유예정(김성은님)</t>
+    <t>20260713 공유(김성은님), 수정필요</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>작성중</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -250,7 +258,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -280,6 +288,9 @@
     </xf>
     <xf numFmtId="14" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -625,7 +636,7 @@
     <col min="5" max="5" width="9.5" style="4" customWidth="1"/>
     <col min="6" max="6" width="9" style="3"/>
     <col min="7" max="7" width="14.75" style="3" customWidth="1"/>
-    <col min="8" max="8" width="28.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="81.25" style="10" customWidth="1"/>
     <col min="9" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
@@ -656,7 +667,7 @@
       <c r="G3" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -674,7 +685,7 @@
       <c r="G4" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="5"/>
+      <c r="H4" s="2"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
@@ -690,7 +701,7 @@
       <c r="G5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H5" s="5"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
@@ -706,7 +717,7 @@
       <c r="G6" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="5"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" s="7">
@@ -730,7 +741,7 @@
       <c r="G7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -756,7 +767,7 @@
       <c r="G8" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="8" t="s">
         <v>35</v>
       </c>
     </row>
@@ -774,7 +785,7 @@
       <c r="G9" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="5"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="10" spans="1:8" ht="34.5" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
@@ -790,7 +801,7 @@
       <c r="G10" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="5"/>
+      <c r="H10" s="2"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
@@ -806,7 +817,7 @@
       <c r="G11" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="5"/>
+      <c r="H11" s="2"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
@@ -822,7 +833,9 @@
       <c r="G12" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H12" s="5"/>
+      <c r="H12" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
@@ -838,7 +851,9 @@
       <c r="G13" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="H13" s="5"/>
+      <c r="H13" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
@@ -862,7 +877,7 @@
       <c r="G14" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H14" s="5"/>
+      <c r="H14" s="2"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
@@ -886,7 +901,9 @@
       <c r="G15" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H15" s="5"/>
+      <c r="H15" s="2" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
@@ -910,7 +927,9 @@
       <c r="G16" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="5"/>
+      <c r="H16" s="2" t="s">
+        <v>37</v>
+      </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
@@ -934,7 +953,7 @@
       <c r="G17" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H17" s="5" t="s">
+      <c r="H17" s="2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -960,7 +979,7 @@
       <c r="G18" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H18" s="5" t="s">
+      <c r="H18" s="2" t="s">
         <v>36</v>
       </c>
     </row>
@@ -986,7 +1005,7 @@
       <c r="G19" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="H19" s="5"/>
+      <c r="H19" s="2"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="7">
@@ -1010,7 +1029,7 @@
       <c r="G20" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="H20" s="7" t="s">
+      <c r="H20" s="8" t="s">
         <v>34</v>
       </c>
     </row>
